--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -595,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -606,7 +606,7 @@
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -617,7 +617,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -633,8 +633,12 @@
       <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="5">
+        <f>C54</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <f xml:space="preserve"> B3</f>
         <v>60000</v>
@@ -650,7 +654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <f xml:space="preserve"> A3 +B4-C4</f>
         <v>242000</v>
@@ -666,7 +670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <f t="shared" ref="A5:A23" si="0" xml:space="preserve"> A4 +B5-C5</f>
         <v>0</v>
@@ -682,7 +686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <f t="shared" si="0"/>
         <v>120000</v>
@@ -698,7 +702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>185000</v>
@@ -714,7 +718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>316000</v>
@@ -730,7 +734,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>16000</v>
@@ -746,7 +750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>116000</v>
@@ -762,7 +766,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>276000</v>
@@ -778,7 +782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>-24000</v>
@@ -794,7 +798,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>183000</v>
@@ -810,7 +814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>335000</v>
@@ -826,7 +830,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>410000</v>
@@ -842,7 +846,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>1010000</v>

--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -169,6 +169,12 @@
   </si>
   <si>
     <t>تخمه</t>
+  </si>
+  <si>
+    <t>1405/06/01</t>
+  </si>
+  <si>
+    <t>لواشک</t>
   </si>
 </sst>
 </file>
@@ -635,7 +641,7 @@
       </c>
       <c r="H2" s="5">
         <f>C54</f>
-        <v>300000</v>
+        <v>425000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1120,17 +1126,23 @@
     <row r="35" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-      <c r="B35" s="9"/>
+        <v>425000</v>
+      </c>
+      <c r="B35" s="9">
+        <v>125000</v>
+      </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="D35" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -1140,7 +1152,7 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -1150,7 +1162,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -1160,7 +1172,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -1170,7 +1182,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1180,7 +1192,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1190,7 +1202,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1200,7 +1212,7 @@
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1210,7 +1222,7 @@
     <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1220,7 +1232,7 @@
     <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1230,7 +1242,7 @@
     <row r="46" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1240,7 +1252,7 @@
     <row r="47" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1250,7 +1262,7 @@
     <row r="48" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="10"/>
@@ -1260,7 +1272,7 @@
     <row r="49" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
@@ -1270,7 +1282,7 @@
     <row r="50" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1280,7 +1292,7 @@
     <row r="51" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1291,7 +1303,7 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12">
         <f xml:space="preserve"> SUM(B31:B51)+B24</f>
-        <v>3163000</v>
+        <v>3288000</v>
       </c>
       <c r="C52" s="12">
         <f xml:space="preserve"> SUM(C31:C51)+C24</f>
@@ -1312,7 +1324,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="13">
         <f>A51</f>
-        <v>300000</v>
+        <v>425000</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>6</v>
